--- a/test_samples/MAERSK/sample1_ref.xlsx
+++ b/test_samples/MAERSK/sample1_ref.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0903164786</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -670,8 +670,10 @@
           <t>JKT3320212</t>
         </is>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>5617840405</v>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
@@ -729,7 +731,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0903164786</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -743,8 +745,10 @@
           <t>JKT3320212</t>
         </is>
       </c>
-      <c r="L3" s="0" t="n">
-        <v>5617840405</v>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
@@ -802,7 +806,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0903164786</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -816,8 +820,10 @@
           <t>JKT3320212</t>
         </is>
       </c>
-      <c r="L4" s="0" t="n">
-        <v>5617840405</v>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
@@ -875,7 +881,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0903164786</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -889,8 +895,10 @@
           <t>JKT3320212</t>
         </is>
       </c>
-      <c r="L5" s="0" t="n">
-        <v>5617840405</v>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
@@ -931,9 +939,6 @@
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="R12" s="1" t="n"/>
     </row>
